--- a/tiflow-core/develop/1.0.0-draft/ValueSet-tiflow-operation-outcome-details-vs.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/ValueSet-tiflow-operation-outcome-details-vs.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -159,6 +159,30 @@
   </si>
   <si>
     <t>unable to allocate resource id</t>
+  </si>
+  <si>
+    <t>MSG_BAD_FORMAT</t>
+  </si>
+  <si>
+    <t>MSG_TIMEOUT</t>
+  </si>
+  <si>
+    <t>MSG_INTERNAL_ERROR</t>
+  </si>
+  <si>
+    <t>MSG_UNKNOWN_TYPE</t>
+  </si>
+  <si>
+    <t>MSG_DELETED</t>
+  </si>
+  <si>
+    <t>MSG_PARAM_UNKNOWN</t>
+  </si>
+  <si>
+    <t>MSG_BAD_SYNTAX</t>
+  </si>
+  <si>
+    <t>MSG_UNKNOWN_OPERATION</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/CodeSystem/operation-outcome</t>
@@ -533,7 +557,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -574,18 +598,66 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>29</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B6" t="s" s="2">
-        <v>48</v>
+      <c r="B14" t="s" s="2">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
